--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2063-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2063-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417B05F6-EA96-4694-89DE-DF289BE1F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D574BF23-C6FE-409E-AAE6-5B4DF9599A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DB1AE8B4-D129-4F0C-B8BD-98C86B8818EA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{43CFB43A-93BF-4F7F-9AE7-498C978A25DF}"/>
   </bookViews>
   <sheets>
     <sheet name="2063-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1508,25 +1508,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9D7E79-924A-47A4-9029-201FAA2DABF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA9D523-68A8-4014-AB16-4A1FDF88F404}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1716,7 +1716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2023</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2022</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2021</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2020</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>29</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>29</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2019</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2018</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2017</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2016</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2015</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2014</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2013</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2012</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2011</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2010</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2009</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>8.64</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2008</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
         <v>57</v>
       </c>
